--- a/outputs/q3/summary.xlsx
+++ b/outputs/q3/summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,41 +503,91 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>标准化总成本</t>
+          <t>期初库存产品当量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>494225.6731101544</v>
+        <v>112800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>实际A类平均占比</t>
+          <t>标准化总成本</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.830190986997636</v>
+        <v>470754.1140151093</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>实际C类平均占比</t>
+          <t>实际A类平均占比</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00232561317966903</v>
+        <v>0.5768751478152595</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>实际C类平均占比</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1322604868248734</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>预测周供货能力最小值</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>21467.31401669093</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>预测周供货能力最大值</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>25289.55944220957</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>计划周发运量最小值</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15088.29595080277</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>计划周发运量最大值</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>19373.92418746005</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>实际最低库存</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>58071.56102358679</v>
+      <c r="B16" t="n">
+        <v>89815.6981543811</v>
       </c>
     </row>
   </sheetData>
